--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136481269</v>
       </c>
       <c r="B9" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136583117</v>
       </c>
       <c r="B10" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136481259</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>136759779</v>
       </c>
       <c r="B31" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>136993468</v>
       </c>
       <c r="B32" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>136993470</v>
       </c>
       <c r="B33" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>136993475</v>
       </c>
       <c r="B34" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136481269</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136583117</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136481259</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136993432</v>
+        <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>80102</v>
+        <v>79242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,34 +2975,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407062</v>
+        <v>407179</v>
       </c>
       <c r="R22" t="n">
-        <v>6850535</v>
+        <v>6850541</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,22 +3033,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,27 +3058,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993432</t>
+          <t>https://artportalen.se/Sighting/137153248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136993435</v>
+        <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,10 +3110,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407040</v>
+        <v>407062</v>
       </c>
       <c r="R23" t="n">
-        <v>6850643</v>
+        <v>6850535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3146,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,16 +3181,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993435</t>
+          <t>https://artportalen.se/Sighting/136993432</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136993472</v>
+        <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,10 +3222,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407125</v>
+        <v>407040</v>
       </c>
       <c r="R24" t="n">
-        <v>6850545</v>
+        <v>6850643</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3258,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3267,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,16 +3293,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993472</t>
+          <t>https://artportalen.se/Sighting/136993435</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136993492</v>
+        <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,10 +3334,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407186</v>
+        <v>407125</v>
       </c>
       <c r="R25" t="n">
-        <v>6850192</v>
+        <v>6850545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3370,7 +3369,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3379,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,16 +3405,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993492</t>
+          <t>https://artportalen.se/Sighting/136993472</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136993482</v>
+        <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,39 +3422,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407175</v>
+        <v>407186</v>
       </c>
       <c r="R26" t="n">
-        <v>6850398</v>
+        <v>6850192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3487,7 +3481,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3497,12 +3491,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,13 +3517,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993482</t>
+          <t>https://artportalen.se/Sighting/136993492</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136993487</v>
+        <v>136993482</v>
       </c>
       <c r="B27" t="n">
         <v>58008</v>
@@ -3565,7 +3554,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3574,10 +3563,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407203</v>
+        <v>407175</v>
       </c>
       <c r="R27" t="n">
-        <v>6850305</v>
+        <v>6850398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3609,7 +3598,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,12 +3608,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>4-5 år gamla ringhack på gran</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,13 +3639,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993487</t>
+          <t>https://artportalen.se/Sighting/136993482</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136993489</v>
+        <v>136993487</v>
       </c>
       <c r="B28" t="n">
         <v>58008</v>
@@ -3687,7 +3676,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3696,10 +3685,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407201</v>
+        <v>407203</v>
       </c>
       <c r="R28" t="n">
-        <v>6850299</v>
+        <v>6850305</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3720,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,12 +3730,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>4-5 år gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,13 +3761,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993489</t>
+          <t>https://artportalen.se/Sighting/136993487</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136993490</v>
+        <v>136993489</v>
       </c>
       <c r="B29" t="n">
         <v>58008</v>
@@ -3809,7 +3798,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3818,10 +3807,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407193</v>
+        <v>407201</v>
       </c>
       <c r="R29" t="n">
-        <v>6850294</v>
+        <v>6850299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3868,7 +3857,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,16 +3883,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993490</t>
+          <t>https://artportalen.se/Sighting/136993489</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136993477</v>
+        <v>136993490</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3911,34 +3900,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407158</v>
+        <v>407193</v>
       </c>
       <c r="R30" t="n">
-        <v>6850444</v>
+        <v>6850294</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3970,7 +3964,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3980,7 +3974,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4006,58 +4005,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993477</t>
+          <t>https://artportalen.se/Sighting/136993490</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136759779</v>
+        <v>136993477</v>
       </c>
       <c r="B31" t="n">
-        <v>98236</v>
+        <v>58169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407211</v>
+        <v>407158</v>
       </c>
       <c r="R31" t="n">
-        <v>6850459</v>
+        <v>6850444</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4081,27 +4076,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4116,27 +4106,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759779</t>
+          <t>https://artportalen.se/Sighting/136993477</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136993468</v>
+        <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,20 +4151,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407153</v>
+        <v>407211</v>
       </c>
       <c r="R32" t="n">
-        <v>6850615</v>
+        <v>6850459</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4198,22 +4192,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,27 +4227,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993468</t>
+          <t>https://artportalen.se/Sighting/136759779</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136993470</v>
+        <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98230</v>
+        <v>98240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,16 +4255,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4280,10 +4279,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407131</v>
+        <v>407153</v>
       </c>
       <c r="R33" t="n">
-        <v>6850605</v>
+        <v>6850615</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4315,7 +4314,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4325,7 +4324,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4351,16 +4350,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993470</t>
+          <t>https://artportalen.se/Sighting/136993468</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136993475</v>
+        <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407152</v>
+        <v>407131</v>
       </c>
       <c r="R34" t="n">
-        <v>6850478</v>
+        <v>6850605</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4427,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4437,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4463,38 +4462,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993475</t>
+          <t>https://artportalen.se/Sighting/136993470</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136993437</v>
+        <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>79241</v>
+        <v>98234</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4504,10 +4503,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407038</v>
+        <v>407152</v>
       </c>
       <c r="R35" t="n">
-        <v>6850644</v>
+        <v>6850478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4539,7 +4538,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4549,7 +4548,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4575,7 +4574,230 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136993475</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136993437</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>407038</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6850644</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136993437</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137153247</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>407176</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6850612</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153247</t>
         </is>
       </c>
     </row>
@@ -4615,6 +4837,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136583117</v>
       </c>
       <c r="B10" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>136993437</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137153247</v>
       </c>
       <c r="B37" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136993482</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>136993487</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136993489</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>136993490</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136993477</v>
       </c>
       <c r="B31" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>136993437</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137153247</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136993482</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>136993487</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136993489</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>136993490</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136993477</v>
       </c>
       <c r="B31" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>136993437</v>
       </c>
       <c r="B36" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137153247</v>
       </c>
       <c r="B37" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -3552,11 +3552,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
@@ -3674,11 +3670,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
@@ -3796,11 +3788,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
@@ -3918,11 +3906,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136993482</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>136993487</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>136993489</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>136993490</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>136993477</v>
       </c>
       <c r="B31" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136993437</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>137153247</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>136759880</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136759882</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136759757</v>
       </c>
       <c r="B16" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>136759779</v>
       </c>
       <c r="B32" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136993482</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>136993487</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>136993489</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>136993490</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>136993477</v>
       </c>
       <c r="B31" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136993437</v>
       </c>
       <c r="B36" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>137153247</v>
       </c>
       <c r="B37" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136993431</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136993433</v>
       </c>
       <c r="B6" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993471</v>
       </c>
       <c r="B7" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993484</v>
       </c>
       <c r="B8" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136993494</v>
       </c>
       <c r="B14" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>136993478</v>
       </c>
       <c r="B15" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>136993476</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136993486</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136993488</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>136993469</v>
       </c>
       <c r="B20" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>136993483</v>
       </c>
       <c r="B21" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137153248</v>
       </c>
       <c r="B22" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136993432</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>136993435</v>
       </c>
       <c r="B24" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136993472</v>
       </c>
       <c r="B25" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136993492</v>
       </c>
       <c r="B26" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136993482</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>136993487</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>136993489</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>136993490</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>136993477</v>
       </c>
       <c r="B31" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>136993468</v>
       </c>
       <c r="B33" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>136993470</v>
       </c>
       <c r="B34" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>136993475</v>
       </c>
       <c r="B35" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>136993437</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>137153247</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136993431</v>
+        <v>137405342</v>
       </c>
       <c r="B5" t="n">
-        <v>91173</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407023</v>
+        <v>407191</v>
       </c>
       <c r="R5" t="n">
-        <v>6850497</v>
+        <v>6850589</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,65 +1111,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993431</t>
+          <t>https://artportalen.se/Sighting/137405342</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136993433</v>
+        <v>137405351</v>
       </c>
       <c r="B6" t="n">
-        <v>92222</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407060</v>
+        <v>407066</v>
       </c>
       <c r="R6" t="n">
-        <v>6850584</v>
+        <v>6850453</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,49 +1223,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993433</t>
+          <t>https://artportalen.se/Sighting/137405351</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136993471</v>
+        <v>136993431</v>
       </c>
       <c r="B7" t="n">
-        <v>96630</v>
+        <v>91173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2812</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407133</v>
+        <v>407023</v>
       </c>
       <c r="R7" t="n">
-        <v>6850589</v>
+        <v>6850497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,38 +1346,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993471</t>
+          <t>https://artportalen.se/Sighting/136993431</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136993484</v>
+        <v>136993433</v>
       </c>
       <c r="B8" t="n">
-        <v>96630</v>
+        <v>92222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407180</v>
+        <v>407060</v>
       </c>
       <c r="R8" t="n">
-        <v>6850383</v>
+        <v>6850584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,58 +1458,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993484</t>
+          <t>https://artportalen.se/Sighting/136993433</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136481269</v>
+        <v>136993471</v>
       </c>
       <c r="B9" t="n">
-        <v>93420</v>
+        <v>96630</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406973</v>
+        <v>407133</v>
       </c>
       <c r="R9" t="n">
-        <v>6850623</v>
+        <v>6850589</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,27 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,69 +1559,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136481269</t>
+          <t>https://artportalen.se/Sighting/136993471</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136583117</v>
+        <v>136993484</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>96630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406975</v>
+        <v>407180</v>
       </c>
       <c r="R10" t="n">
-        <v>6850621</v>
+        <v>6850383</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,17 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,27 +1671,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583117</t>
+          <t>https://artportalen.se/Sighting/136993484</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136481259</v>
+        <v>136481269</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1735,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406987</v>
+        <v>406973</v>
       </c>
       <c r="R11" t="n">
-        <v>6850613</v>
+        <v>6850623</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1811,16 +1803,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136481259</t>
+          <t>https://artportalen.se/Sighting/136481269</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136759880</v>
+        <v>136583117</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,26 +1820,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1856,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407078</v>
+        <v>406975</v>
       </c>
       <c r="R12" t="n">
-        <v>6850524</v>
+        <v>6850621</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,22 +1878,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1932,16 +1914,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759880</t>
+          <t>https://artportalen.se/Sighting/136583117</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136759882</v>
+        <v>136481259</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1977,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406974</v>
+        <v>406987</v>
       </c>
       <c r="R13" t="n">
-        <v>6850570</v>
+        <v>6850613</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,22 +1989,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2053,16 +2035,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759882</t>
+          <t>https://artportalen.se/Sighting/136481259</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136993494</v>
+        <v>136759880</v>
       </c>
       <c r="B14" t="n">
-        <v>93469</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,20 +2069,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407194</v>
+        <v>407078</v>
       </c>
       <c r="R14" t="n">
-        <v>6850178</v>
+        <v>6850524</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,22 +2110,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,65 +2145,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993494</t>
+          <t>https://artportalen.se/Sighting/136759880</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136993478</v>
+        <v>136759882</v>
       </c>
       <c r="B15" t="n">
-        <v>93140</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407155</v>
+        <v>406974</v>
       </c>
       <c r="R15" t="n">
-        <v>6850448</v>
+        <v>6850570</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,22 +2231,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,27 +2266,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993478</t>
+          <t>https://artportalen.se/Sighting/136759882</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136759757</v>
+        <v>136993494</v>
       </c>
       <c r="B16" t="n">
-        <v>92180</v>
+        <v>93469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,41 +2294,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406975</v>
+        <v>407194</v>
       </c>
       <c r="R16" t="n">
-        <v>6850559</v>
+        <v>6850178</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,27 +2348,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,65 +2378,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759757</t>
+          <t>https://artportalen.se/Sighting/136993494</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136993476</v>
+        <v>137405318</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>93469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407155</v>
+        <v>407038</v>
       </c>
       <c r="R17" t="n">
-        <v>6850466</v>
+        <v>6850562</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,22 +2460,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,65 +2490,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993476</t>
+          <t>https://artportalen.se/Sighting/137405318</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136993486</v>
+        <v>137405344</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407192</v>
+        <v>407185</v>
       </c>
       <c r="R18" t="n">
-        <v>6850349</v>
+        <v>6850564</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2581,22 +2572,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,65 +2602,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993486</t>
+          <t>https://artportalen.se/Sighting/137405344</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136993488</v>
+        <v>137405357</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>93469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407200</v>
+        <v>407051</v>
       </c>
       <c r="R19" t="n">
-        <v>6850323</v>
+        <v>6850403</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,22 +2684,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,27 +2714,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993488</t>
+          <t>https://artportalen.se/Sighting/137405357</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136993469</v>
+        <v>137405358</v>
       </c>
       <c r="B20" t="n">
-        <v>78924</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,37 +2742,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407151</v>
+        <v>407066</v>
       </c>
       <c r="R20" t="n">
-        <v>6850617</v>
+        <v>6850359</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2805,22 +2796,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,27 +2826,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993469</t>
+          <t>https://artportalen.se/Sighting/137405358</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136993483</v>
+        <v>137405384</v>
       </c>
       <c r="B21" t="n">
-        <v>83512</v>
+        <v>93469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,37 +2854,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407192</v>
+        <v>406974</v>
       </c>
       <c r="R21" t="n">
-        <v>6850349</v>
+        <v>6850435</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2917,22 +2908,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,69 +2938,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993483</t>
+          <t>https://artportalen.se/Sighting/137405384</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137153248</v>
+        <v>137405383</v>
       </c>
       <c r="B22" t="n">
-        <v>79278</v>
+        <v>93473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407179</v>
+        <v>406976</v>
       </c>
       <c r="R22" t="n">
-        <v>6850541</v>
+        <v>6850423</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3033,17 +3020,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,49 +3050,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153248</t>
+          <t>https://artportalen.se/Sighting/137405383</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136993432</v>
+        <v>136993478</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>93140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3110,10 +3102,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407062</v>
+        <v>407155</v>
       </c>
       <c r="R23" t="n">
-        <v>6850535</v>
+        <v>6850448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3145,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,16 +3173,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993432</t>
+          <t>https://artportalen.se/Sighting/136993478</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136993435</v>
+        <v>136759757</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>92180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,37 +3190,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407040</v>
+        <v>406975</v>
       </c>
       <c r="R24" t="n">
-        <v>6850643</v>
+        <v>6850559</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,22 +3248,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3282,27 +3283,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993435</t>
+          <t>https://artportalen.se/Sighting/136759757</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136993472</v>
+        <v>137405385</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>93495</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,37 +3311,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407125</v>
+        <v>406964</v>
       </c>
       <c r="R25" t="n">
-        <v>6850545</v>
+        <v>6850513</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3364,22 +3365,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3394,49 +3395,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993472</t>
+          <t>https://artportalen.se/Sighting/137405385</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136993492</v>
+        <v>136993476</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3446,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407186</v>
+        <v>407155</v>
       </c>
       <c r="R26" t="n">
-        <v>6850192</v>
+        <v>6850466</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3481,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3491,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,52 +3518,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993492</t>
+          <t>https://artportalen.se/Sighting/136993476</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136993482</v>
+        <v>136993486</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>407175</v>
+        <v>407192</v>
       </c>
       <c r="R27" t="n">
-        <v>6850398</v>
+        <v>6850349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,12 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,52 +3630,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993482</t>
+          <t>https://artportalen.se/Sighting/136993486</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136993487</v>
+        <v>136993488</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>407203</v>
+        <v>407200</v>
       </c>
       <c r="R28" t="n">
-        <v>6850305</v>
+        <v>6850323</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3725,11 +3719,6 @@
           <t>14:14</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>4-5 år gamla ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3753,55 +3742,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993487</t>
+          <t>https://artportalen.se/Sighting/136993488</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136993489</v>
+        <v>137405347</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>407201</v>
+        <v>407178</v>
       </c>
       <c r="R29" t="n">
-        <v>6850299</v>
+        <v>6850477</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3825,27 +3813,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,66 +3843,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993489</t>
+          <t>https://artportalen.se/Sighting/137405347</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136993490</v>
+        <v>137405349</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>407193</v>
+        <v>407131</v>
       </c>
       <c r="R30" t="n">
-        <v>6850294</v>
+        <v>6850451</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3943,27 +3925,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3978,65 +3955,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993490</t>
+          <t>https://artportalen.se/Sighting/137405349</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136993477</v>
+        <v>137405350</v>
       </c>
       <c r="B31" t="n">
-        <v>58196</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>407158</v>
+        <v>407109</v>
       </c>
       <c r="R31" t="n">
-        <v>6850444</v>
+        <v>6850441</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4060,22 +4037,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4090,69 +4067,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993477</t>
+          <t>https://artportalen.se/Sighting/137405350</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136759779</v>
+        <v>136993469</v>
       </c>
       <c r="B32" t="n">
-        <v>98273</v>
+        <v>78924</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>407211</v>
+        <v>407151</v>
       </c>
       <c r="R32" t="n">
-        <v>6850459</v>
+        <v>6850617</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4176,27 +4149,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,65 +4179,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759779</t>
+          <t>https://artportalen.se/Sighting/136993469</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136993468</v>
+        <v>137405346</v>
       </c>
       <c r="B33" t="n">
-        <v>98286</v>
+        <v>78924</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407153</v>
+        <v>407205</v>
       </c>
       <c r="R33" t="n">
-        <v>6850615</v>
+        <v>6850499</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4293,22 +4261,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,65 +4291,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993468</t>
+          <t>https://artportalen.se/Sighting/137405346</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136993470</v>
+        <v>137405355</v>
       </c>
       <c r="B34" t="n">
-        <v>98280</v>
+        <v>78924</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>407131</v>
+        <v>407013</v>
       </c>
       <c r="R34" t="n">
-        <v>6850605</v>
+        <v>6850456</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4405,22 +4373,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,49 +4403,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993470</t>
+          <t>https://artportalen.se/Sighting/137405355</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136993475</v>
+        <v>136993483</v>
       </c>
       <c r="B35" t="n">
-        <v>98280</v>
+        <v>83512</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4487,10 +4455,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>407152</v>
+        <v>407192</v>
       </c>
       <c r="R35" t="n">
-        <v>6850478</v>
+        <v>6850349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4522,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4532,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4558,16 +4526,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993475</t>
+          <t>https://artportalen.se/Sighting/136993483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136993437</v>
+        <v>137153248</v>
       </c>
       <c r="B36" t="n">
-        <v>79279</v>
+        <v>79278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4575,34 +4543,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storänget, Dlr</t>
+          <t>Dyvelblästan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>407038</v>
+        <v>407179</v>
       </c>
       <c r="R36" t="n">
-        <v>6850644</v>
+        <v>6850541</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4629,22 +4601,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,27 +4626,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993437</t>
+          <t>https://artportalen.se/Sighting/137153248</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137153247</v>
+        <v>137405352</v>
       </c>
       <c r="B37" t="n">
-        <v>79279</v>
+        <v>79278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4687,41 +4654,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dyvelblästan, Dlr</t>
+          <t>Norr Storänget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>407176</v>
+        <v>407018</v>
       </c>
       <c r="R37" t="n">
-        <v>6850612</v>
+        <v>6850455</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4745,17 +4708,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,18 +4738,2627 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137405352</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136993432</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>407062</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6850535</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993432</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136993435</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>407040</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6850643</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993435</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136993472</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>407125</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6850545</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993472</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136993492</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>407186</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6850192</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993492</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137405343</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>407190</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6850592</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405343</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137405345</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>407200</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6850555</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405345</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137405382</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>406981</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6850420</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405382</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137405356</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78521</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>407013</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6850453</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405356</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136993482</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>407175</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6850398</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993482</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136993487</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>407203</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6850305</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4-5 år gamla ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993487</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136993489</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>407201</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6850299</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993489</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136993490</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>407193</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6850294</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993490</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136993477</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>407158</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6850444</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993477</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136759779</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98273</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>407211</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6850459</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759779</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136993468</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98286</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>407153</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6850615</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993468</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136993470</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98280</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>407131</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6850605</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993470</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136993475</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98280</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>407152</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6850478</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993475</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136993437</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>407038</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6850644</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993437</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137153247</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Dyvelblästan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>407176</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6850612</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137153247</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137405353</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>407015</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6850458</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405353</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137405354</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>407015</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6850458</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405354</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137405348</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>407140</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6850463</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405348</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137405380</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norr Storänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>406989</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6850408</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405380</t>
         </is>
       </c>
     </row>
@@ -4823,6 +7400,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137405342</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137405351</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993431</v>
       </c>
       <c r="B7" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993433</v>
       </c>
       <c r="B8" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993471</v>
       </c>
       <c r="B9" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993484</v>
       </c>
       <c r="B10" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136993494</v>
       </c>
       <c r="B16" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>137405318</v>
       </c>
       <c r="B17" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>137405344</v>
       </c>
       <c r="B18" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137405357</v>
       </c>
       <c r="B19" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137405358</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>137405384</v>
       </c>
       <c r="B21" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>137405383</v>
       </c>
       <c r="B22" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>136993478</v>
       </c>
       <c r="B23" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>137405385</v>
       </c>
       <c r="B25" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>136993476</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136993486</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>136993488</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>137405347</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>137405349</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>137405350</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>136993469</v>
       </c>
       <c r="B32" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>137405346</v>
       </c>
       <c r="B33" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>137405355</v>
       </c>
       <c r="B34" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>136993483</v>
       </c>
       <c r="B35" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137153248</v>
       </c>
       <c r="B36" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>137405352</v>
       </c>
       <c r="B37" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>136993432</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>136993435</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>136993472</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>136993492</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>137405343</v>
       </c>
       <c r="B42" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137405345</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>137405382</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>137405356</v>
       </c>
       <c r="B45" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136993468</v>
       </c>
       <c r="B52" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>136993470</v>
       </c>
       <c r="B53" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>136993475</v>
       </c>
       <c r="B54" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>136993437</v>
       </c>
       <c r="B55" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137153247</v>
       </c>
       <c r="B56" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>137405353</v>
       </c>
       <c r="B57" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>137405354</v>
       </c>
       <c r="B58" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>137405348</v>
       </c>
       <c r="B59" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>137405380</v>
       </c>
       <c r="B60" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137405342</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137405351</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993431</v>
       </c>
       <c r="B7" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993433</v>
       </c>
       <c r="B8" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993471</v>
       </c>
       <c r="B9" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993484</v>
       </c>
       <c r="B10" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136993494</v>
       </c>
       <c r="B16" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>137405318</v>
       </c>
       <c r="B17" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>137405344</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137405357</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137405358</v>
       </c>
       <c r="B20" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>137405384</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>137405383</v>
       </c>
       <c r="B22" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>136993478</v>
       </c>
       <c r="B23" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>137405385</v>
       </c>
       <c r="B25" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>136993476</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136993486</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>136993488</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>137405347</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>137405349</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>137405350</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>136993469</v>
       </c>
       <c r="B32" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>137405346</v>
       </c>
       <c r="B33" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>137405355</v>
       </c>
       <c r="B34" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>136993483</v>
       </c>
       <c r="B35" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137153248</v>
       </c>
       <c r="B36" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>137405352</v>
       </c>
       <c r="B37" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>136993432</v>
       </c>
       <c r="B38" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>136993435</v>
       </c>
       <c r="B39" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>136993472</v>
       </c>
       <c r="B40" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>136993492</v>
       </c>
       <c r="B41" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>137405343</v>
       </c>
       <c r="B42" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137405345</v>
       </c>
       <c r="B43" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>137405382</v>
       </c>
       <c r="B44" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>137405356</v>
       </c>
       <c r="B45" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136993468</v>
       </c>
       <c r="B52" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>136993470</v>
       </c>
       <c r="B53" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>136993475</v>
       </c>
       <c r="B54" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>136993437</v>
       </c>
       <c r="B55" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137153247</v>
       </c>
       <c r="B56" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>137405353</v>
       </c>
       <c r="B57" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>137405354</v>
       </c>
       <c r="B58" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>137405348</v>
       </c>
       <c r="B59" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>137405380</v>
       </c>
       <c r="B60" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137405342</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137405351</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993431</v>
       </c>
       <c r="B7" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993433</v>
       </c>
       <c r="B8" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993471</v>
       </c>
       <c r="B9" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993484</v>
       </c>
       <c r="B10" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136993494</v>
       </c>
       <c r="B16" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>137405318</v>
       </c>
       <c r="B17" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>137405344</v>
       </c>
       <c r="B18" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137405357</v>
       </c>
       <c r="B19" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137405358</v>
       </c>
       <c r="B20" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>137405384</v>
       </c>
       <c r="B21" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>137405383</v>
       </c>
       <c r="B22" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>136993478</v>
       </c>
       <c r="B23" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>137405385</v>
       </c>
       <c r="B25" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>136993476</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136993486</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>136993488</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>137405347</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>137405349</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>137405350</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>136993469</v>
       </c>
       <c r="B32" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>137405346</v>
       </c>
       <c r="B33" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>137405355</v>
       </c>
       <c r="B34" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>136993483</v>
       </c>
       <c r="B35" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137153248</v>
       </c>
       <c r="B36" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>137405352</v>
       </c>
       <c r="B37" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>136993432</v>
       </c>
       <c r="B38" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>136993435</v>
       </c>
       <c r="B39" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>136993472</v>
       </c>
       <c r="B40" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>136993492</v>
       </c>
       <c r="B41" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>137405343</v>
       </c>
       <c r="B42" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137405345</v>
       </c>
       <c r="B43" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>137405382</v>
       </c>
       <c r="B44" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>137405356</v>
       </c>
       <c r="B45" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136993468</v>
       </c>
       <c r="B52" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>136993470</v>
       </c>
       <c r="B53" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>136993475</v>
       </c>
       <c r="B54" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>136993437</v>
       </c>
       <c r="B55" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137153247</v>
       </c>
       <c r="B56" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>137405353</v>
       </c>
       <c r="B57" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>137405354</v>
       </c>
       <c r="B58" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>137405348</v>
       </c>
       <c r="B59" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>137405380</v>
       </c>
       <c r="B60" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993431</v>
       </c>
       <c r="B7" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993433</v>
       </c>
       <c r="B8" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993471</v>
       </c>
       <c r="B9" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993484</v>
       </c>
       <c r="B10" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136993494</v>
       </c>
       <c r="B16" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>136993478</v>
       </c>
       <c r="B23" t="n">
-        <v>93156</v>
+        <v>93157</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>136993476</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136993486</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>136993488</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>136993469</v>
       </c>
       <c r="B32" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>136993483</v>
       </c>
       <c r="B35" t="n">
-        <v>83526</v>
+        <v>83527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>136993432</v>
       </c>
       <c r="B38" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>136993435</v>
       </c>
       <c r="B39" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>136993472</v>
       </c>
       <c r="B40" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>136993492</v>
       </c>
       <c r="B41" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136993468</v>
       </c>
       <c r="B52" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>136993470</v>
       </c>
       <c r="B53" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>136993475</v>
       </c>
       <c r="B54" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>136993437</v>
       </c>
       <c r="B55" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2026 artfynd.xlsx
+++ b/artfynd/A 41583-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136993473</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136993474</v>
       </c>
       <c r="B3" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136993493</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137405342</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137405351</v>
       </c>
       <c r="B6" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136993431</v>
       </c>
       <c r="B7" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136993433</v>
       </c>
       <c r="B8" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136993471</v>
       </c>
       <c r="B9" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136993484</v>
       </c>
       <c r="B10" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136993494</v>
       </c>
       <c r="B16" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>137405318</v>
       </c>
       <c r="B17" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>137405344</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137405357</v>
       </c>
       <c r="B19" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137405358</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>137405384</v>
       </c>
       <c r="B21" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>137405383</v>
       </c>
       <c r="B22" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>136993478</v>
       </c>
       <c r="B23" t="n">
-        <v>93157</v>
+        <v>93160</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>137405385</v>
       </c>
       <c r="B25" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>136993476</v>
       </c>
       <c r="B26" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136993486</v>
       </c>
       <c r="B27" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>136993488</v>
       </c>
       <c r="B28" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>137405347</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>137405349</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>137405350</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>136993469</v>
       </c>
       <c r="B32" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>137405346</v>
       </c>
       <c r="B33" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>137405355</v>
       </c>
       <c r="B34" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>136993483</v>
       </c>
       <c r="B35" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>137153248</v>
       </c>
       <c r="B36" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>137405352</v>
       </c>
       <c r="B37" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>136993432</v>
       </c>
       <c r="B38" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>136993435</v>
       </c>
       <c r="B39" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>136993472</v>
       </c>
       <c r="B40" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>136993492</v>
       </c>
       <c r="B41" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>137405343</v>
       </c>
       <c r="B42" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137405345</v>
       </c>
       <c r="B43" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>137405382</v>
       </c>
       <c r="B44" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>137405356</v>
       </c>
       <c r="B45" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>136993482</v>
       </c>
       <c r="B46" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>136993487</v>
       </c>
       <c r="B47" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>136993489</v>
       </c>
       <c r="B48" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>136993490</v>
       </c>
       <c r="B49" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>136993477</v>
       </c>
       <c r="B50" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>136993468</v>
       </c>
       <c r="B52" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>136993470</v>
       </c>
       <c r="B53" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>136993475</v>
       </c>
       <c r="B54" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>136993437</v>
       </c>
       <c r="B55" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137153247</v>
       </c>
       <c r="B56" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>137405353</v>
       </c>
       <c r="B57" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>137405354</v>
       </c>
       <c r="B58" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>137405348</v>
       </c>
       <c r="B59" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>137405380</v>
       </c>
       <c r="B60" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
